--- a/ConfigWorkspace/Data/element_duo_reaction.xlsx
+++ b/ConfigWorkspace/Data/element_duo_reaction.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>

--- a/ConfigWorkspace/Data/element_duo_reaction.xlsx
+++ b/ConfigWorkspace/Data/element_duo_reaction.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F9E27A-7E42-4BFF-ACD8-B082E7E451F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30C55093-4F16-4A80-92A9-27FE8E5A38C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3945" yWindow="3810" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -112,6 +112,36 @@
   </si>
   <si>
     <t>FALSE</t>
+  </si>
+  <si>
+    <t>基础火池</t>
+  </si>
+  <si>
+    <t>基础冰面</t>
+  </si>
+  <si>
+    <t>基础电源</t>
+  </si>
+  <si>
+    <t>基础植物区</t>
+  </si>
+  <si>
+    <t>燎原火海</t>
+  </si>
+  <si>
+    <t>带电荆棘</t>
+  </si>
+  <si>
+    <t>霜冻冰刺</t>
+  </si>
+  <si>
+    <t>蒸汽</t>
+  </si>
+  <si>
+    <t>结冰</t>
+  </si>
+  <si>
+    <t>空地</t>
   </si>
 </sst>
 </file>
@@ -459,15 +489,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="6" width="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.26953125" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -499,7 +529,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -531,7 +561,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -563,7 +593,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -595,18 +625,18 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5">
-        <v>16</v>
-      </c>
-      <c r="D5">
-        <v>19</v>
-      </c>
-      <c r="E5">
-        <v>21</v>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -624,18 +654,18 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6">
-        <v>16</v>
-      </c>
-      <c r="D6">
-        <v>18</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
       </c>
       <c r="F6">
         <v>4</v>
@@ -653,18 +683,18 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>3</v>
       </c>
-      <c r="C7">
-        <v>17</v>
-      </c>
-      <c r="D7">
-        <v>18</v>
-      </c>
-      <c r="E7">
-        <v>5</v>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" t="s">
+        <v>37</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -682,18 +712,18 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>4</v>
       </c>
-      <c r="C8">
-        <v>18</v>
-      </c>
-      <c r="D8">
-        <v>19</v>
-      </c>
-      <c r="E8">
-        <v>22</v>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>34</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -711,18 +741,18 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>5</v>
       </c>
-      <c r="C9">
-        <v>17</v>
-      </c>
-      <c r="D9">
-        <v>16</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -740,18 +770,18 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>6</v>
       </c>
-      <c r="C10">
-        <v>17</v>
-      </c>
-      <c r="D10">
-        <v>19</v>
-      </c>
-      <c r="E10">
-        <v>23</v>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" t="s">
+        <v>35</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -771,6 +801,11 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576 E1:E1048576" xr:uid="{1F1FC2BB-DAC7-48AC-9F56-5024F8ADCEDD}">
+      <formula1>"空地,普通泥浆,稀泥,结冰,陶砖,蒸汽,基础水,基础土,基础火池,基础冰面,基础电源,基础植物区,导电区,燎原火海,带电荆棘,霜冻冰刺"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/ConfigWorkspace/Data/element_duo_reaction.xlsx
+++ b/ConfigWorkspace/Data/element_duo_reaction.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30C55093-4F16-4A80-92A9-27FE8E5A38C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E3D8AE0-81B1-4381-86CB-56980D4D5723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -142,6 +142,34 @@
   </si>
   <si>
     <t>空地</t>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pull_strength</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>向心吸引力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>break_aggro</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否清仇恨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -184,8 +212,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -488,314 +519,378 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N10"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="3" max="6" width="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="6" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="15" style="1" customWidth="1"/>
+    <col min="12" max="12" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B5">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
         <v>3</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>1</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B6">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>4</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>4</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>2</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>1.5</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B7">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B7" s="1">
         <v>3</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
         <v>4</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>2.5</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="1">
+        <v>5</v>
+      </c>
+      <c r="K7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B8">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B8" s="1">
         <v>4</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>1</v>
       </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
         <v>3</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="1">
         <v>1</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="1">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B9">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B9" s="1">
         <v>5</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
         <v>6</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="1">
         <v>2.5</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B10">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B10" s="1">
         <v>6</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>1</v>
       </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
         <v>3</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="1">
         <v>1</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1" t="s">
         <v>28</v>
       </c>
     </row>

--- a/ConfigWorkspace/Data/element_duo_reaction.xlsx
+++ b/ConfigWorkspace/Data/element_duo_reaction.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E3D8AE0-81B1-4381-86CB-56980D4D5723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72433C7C-4BC9-4787-B7AB-C0F17F763286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6460" yWindow="1460" windowWidth="15080" windowHeight="11670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -139,9 +139,6 @@
   </si>
   <si>
     <t>结冰</t>
-  </si>
-  <si>
-    <t>空地</t>
   </si>
   <si>
     <t>float</t>
@@ -169,6 +166,10 @@
   </si>
   <si>
     <t>是否清仇恨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FALSH</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -520,19 +521,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N10"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="6" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="15" style="1" customWidth="1"/>
     <col min="12" max="12" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -561,16 +562,16 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -599,16 +600,16 @@
         <v>13</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
@@ -637,16 +638,16 @@
         <v>16</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -675,16 +676,16 @@
         <v>25</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -719,7 +720,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>2</v>
       </c>
@@ -736,7 +737,7 @@
         <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="H6" s="1">
         <v>2</v>
@@ -754,7 +755,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>3</v>
       </c>
@@ -789,7 +790,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>4</v>
       </c>
@@ -824,7 +825,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>5</v>
       </c>
@@ -835,31 +836,31 @@
         <v>29</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H9" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I9" s="1">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J9" s="1">
         <v>0</v>
       </c>
-      <c r="K9" s="1" t="b">
-        <v>1</v>
+      <c r="K9" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>6</v>
       </c>

--- a/ConfigWorkspace/Data/element_duo_reaction.xlsx
+++ b/ConfigWorkspace/Data/element_duo_reaction.xlsx
@@ -169,7 +169,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>FALSH</t>
+    <t>FALSE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -737,7 +737,7 @@
         <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="H6" s="1">
         <v>2</v>
@@ -842,7 +842,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="H9" s="1">
         <v>3</v>

--- a/ConfigWorkspace/Data/element_duo_reaction.xlsx
+++ b/ConfigWorkspace/Data/element_duo_reaction.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E3D8AE0-81B1-4381-86CB-56980D4D5723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72433C7C-4BC9-4787-B7AB-C0F17F763286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6460" yWindow="1460" windowWidth="15080" windowHeight="11670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -139,9 +139,6 @@
   </si>
   <si>
     <t>结冰</t>
-  </si>
-  <si>
-    <t>空地</t>
   </si>
   <si>
     <t>float</t>
@@ -169,6 +166,10 @@
   </si>
   <si>
     <t>是否清仇恨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FALSE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -520,19 +521,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N10"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="6" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="15" style="1" customWidth="1"/>
     <col min="12" max="12" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -561,16 +562,16 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -599,16 +600,16 @@
         <v>13</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
@@ -637,16 +638,16 @@
         <v>16</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -675,16 +676,16 @@
         <v>25</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -719,7 +720,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>2</v>
       </c>
@@ -754,7 +755,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>3</v>
       </c>
@@ -789,7 +790,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>4</v>
       </c>
@@ -824,7 +825,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>5</v>
       </c>
@@ -835,31 +836,31 @@
         <v>29</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="H9" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I9" s="1">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J9" s="1">
         <v>0</v>
       </c>
-      <c r="K9" s="1" t="b">
-        <v>1</v>
+      <c r="K9" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>6</v>
       </c>

--- a/ConfigWorkspace/Data/element_duo_reaction.xlsx
+++ b/ConfigWorkspace/Data/element_duo_reaction.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityHub\Unity Project\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72433C7C-4BC9-4787-B7AB-C0F17F763286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB94DAD-5A78-4B1F-A244-2DCEA712A459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6460" yWindow="1460" windowWidth="15080" windowHeight="11670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3168" yWindow="1812" windowWidth="17280" windowHeight="11448" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -521,12 +521,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N10"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="6" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="15" style="1" customWidth="1"/>
     <col min="12" max="12" width="15" style="1" bestFit="1" customWidth="1"/>
@@ -769,7 +769,7 @@
         <v>37</v>
       </c>
       <c r="F7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>

--- a/ConfigWorkspace/Data/element_duo_reaction.xlsx
+++ b/ConfigWorkspace/Data/element_duo_reaction.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityHub\Unity Project\deepseaoil\ConfigWorkspace\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB94DAD-5A78-4B1F-A244-2DCEA712A459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F546A28-A36D-48BB-A772-699B6995B88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3168" yWindow="1812" windowWidth="17280" windowHeight="11448" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6660" yWindow="4470" windowWidth="21555" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -520,20 +520,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N11"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="6" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.25" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="15" style="1" customWidth="1"/>
     <col min="12" max="12" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -571,7 +571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -609,7 +609,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
@@ -647,7 +647,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -685,7 +685,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -720,7 +720,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B6" s="1">
         <v>2</v>
       </c>
@@ -728,22 +728,22 @@
         <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F6" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" s="1">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
@@ -751,37 +751,37 @@
       <c r="K6" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L6" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F7" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I7" s="1">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J7" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1" t="b">
         <v>0</v>
@@ -790,18 +790,18 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B8" s="1">
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="E8" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F8" s="1">
         <v>1</v>
@@ -810,57 +810,57 @@
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8" s="1">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J8" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K8" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B9" s="1">
         <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F9" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="H9" s="1">
         <v>3</v>
       </c>
       <c r="I9" s="1">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J9" s="1">
         <v>0</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>45</v>
+      <c r="K9" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B10" s="1">
         <v>6</v>
       </c>
@@ -868,37 +868,72 @@
         <v>30</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F10" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="H10" s="1">
         <v>3</v>
       </c>
       <c r="I10" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B11" s="1">
+        <v>7</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="1">
         <v>1</v>
       </c>
-      <c r="J10" s="1">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" s="1" t="s">
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>3</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>28</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576 E1:E1048576" xr:uid="{1F1FC2BB-DAC7-48AC-9F56-5024F8ADCEDD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:E11 C12:E1048576" xr:uid="{1F1FC2BB-DAC7-48AC-9F56-5024F8ADCEDD}">
       <formula1>"空地,普通泥浆,稀泥,结冰,陶砖,蒸汽,基础水,基础土,基础火池,基础冰面,基础电源,基础植物区,导电区,燎原火海,带电荆棘,霜冻冰刺"</formula1>
     </dataValidation>
   </dataValidations>
